--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prep53\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B648F244-FFE4-4668-B7CF-2A28D35B66FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -194,7 +193,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -299,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -346,6 +345,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -446,23 +458,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -498,23 +493,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -690,7 +668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -989,7 +967,7 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="10"/>
+      <c r="B8" s="23"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1051,7 +1029,7 @@
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="10"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -1111,7 +1089,7 @@
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="10"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1171,7 +1149,7 @@
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1201,7 +1179,7 @@
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="10"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1231,7 +1209,7 @@
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -1291,7 +1269,7 @@
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="10"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -1321,7 +1299,7 @@
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="10"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -1351,7 +1329,7 @@
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="10"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -1381,7 +1359,7 @@
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="10"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -1411,7 +1389,7 @@
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="10"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
@@ -1473,7 +1451,7 @@
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="14"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -1503,7 +1481,7 @@
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
@@ -1533,7 +1511,7 @@
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1576,7 +1554,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
+  <sortState ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1585,7 +1563,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1595,7 +1573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Бойков П-40 2027\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A797EDB9-1CBA-47A9-BE1D-9158D01B14DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -193,7 +194,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -351,13 +352,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -458,6 +459,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -493,6 +511,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -668,7 +703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -967,7 +1002,7 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="23"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1089,7 +1124,7 @@
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1179,7 +1214,7 @@
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="26"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1209,7 +1244,7 @@
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="25"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -1329,7 +1364,7 @@
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="23"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -1359,7 +1394,7 @@
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="26"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
@@ -1451,7 +1486,7 @@
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="25"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -1511,7 +1546,7 @@
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="24"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1554,7 +1589,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1563,7 +1598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1573,7 +1608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Бойков П-40 2027\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A797EDB9-1CBA-47A9-BE1D-9158D01B14DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C725FD1F-77E8-4956-8F28-87F228DE3F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,11 +18,6 @@
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -195,7 +190,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +230,15 @@
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -299,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -318,18 +322,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -359,6 +361,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -384,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -424,9 +436,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -459,26 +471,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -511,26 +506,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -735,7 +713,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
@@ -753,37 +731,37 @@
       <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="17" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="7" t="s">
@@ -823,7 +801,7 @@
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="10"/>
+      <c r="B2" s="20"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -841,19 +819,17 @@
       <c r="Q2" s="10"/>
       <c r="R2" s="11"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="10"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -871,18 +847,17 @@
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="10"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B4" s="18"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -900,19 +875,17 @@
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="10"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -930,19 +903,17 @@
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="10"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -960,19 +931,17 @@
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="10"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -990,20 +959,18 @@
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="10"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1020,19 +987,17 @@
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="10"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -1052,20 +1017,18 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="10"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -1073,7 +1036,6 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
-      <c r="K10" s="13"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
@@ -1082,19 +1044,17 @@
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="10"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1112,20 +1072,18 @@
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="10"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -1142,19 +1100,17 @@
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="10"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1172,20 +1128,18 @@
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="10"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -1202,20 +1156,18 @@
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="10"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1232,20 +1184,18 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="12"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -1262,19 +1212,17 @@
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -1292,20 +1240,18 @@
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="10"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -1322,20 +1268,18 @@
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="10"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -1352,20 +1296,18 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="10"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -1382,25 +1324,23 @@
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
       <c r="S20" s="10"/>
-      <c r="T20" s="12"/>
-      <c r="U20" s="12"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="10"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="14"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1412,20 +1352,18 @@
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="13"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B22" s="23"/>
-      <c r="C22" s="10"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -1442,19 +1380,17 @@
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="10"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="13"/>
-      <c r="Z22" s="13"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="10"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
@@ -1474,20 +1410,18 @@
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="10"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="13"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="10"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -1504,20 +1438,18 @@
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="13"/>
-      <c r="Z24" s="13"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -1534,20 +1466,18 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="3"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="28"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1570,20 +1500,20 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B29" s="18"/>
       <c r="C29" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B30" s="21"/>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B30" s="19"/>
       <c r="C30" s="1" t="s">
         <v>52</v>
       </c>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C725FD1F-77E8-4956-8F28-87F228DE3F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -189,7 +188,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -396,9 +395,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -436,9 +435,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -473,7 +472,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -508,7 +507,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,7 +680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -716,7 +715,7 @@
       <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1195,7 +1194,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="22"/>
-      <c r="C16" s="21"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -1519,7 +1518,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
+  <sortState ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1528,7 +1527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1538,7 +1537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1638786-0405-41BD-AA37-EC68E5706618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -188,7 +189,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -395,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -435,9 +436,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -472,7 +473,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -507,7 +508,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -680,7 +681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -801,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="20"/>
-      <c r="C2" s="10"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
@@ -829,7 +830,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="23"/>
-      <c r="C3" s="10"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -857,7 +858,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="18"/>
-      <c r="C4" s="10"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
@@ -885,7 +886,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="23"/>
-      <c r="C5" s="10"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
@@ -913,7 +914,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="20"/>
-      <c r="C6" s="10"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -941,7 +942,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="23"/>
-      <c r="C7" s="10"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -971,7 +972,7 @@
       <c r="B8" s="23"/>
       <c r="C8" s="26"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -997,7 +998,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="21"/>
-      <c r="C9" s="10"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1029,7 +1030,7 @@
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -1054,7 +1055,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="20"/>
-      <c r="C11" s="10"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -1084,7 +1085,7 @@
       <c r="B12" s="23"/>
       <c r="C12" s="20"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="20"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -1110,7 +1111,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="23"/>
-      <c r="C13" s="10"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1140,7 +1141,7 @@
       <c r="B14" s="21"/>
       <c r="C14" s="20"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -1168,7 +1169,7 @@
       <c r="B15" s="23"/>
       <c r="C15" s="21"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -1196,7 +1197,7 @@
       <c r="B16" s="22"/>
       <c r="C16" s="23"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="E16" s="21"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
@@ -1222,7 +1223,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="20"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -1280,7 +1281,7 @@
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="E19" s="20"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -1308,7 +1309,7 @@
       <c r="B20" s="23"/>
       <c r="C20" s="21"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -1336,7 +1337,7 @@
       <c r="B21" s="23"/>
       <c r="C21" s="21"/>
       <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="10"/>
       <c r="G21" s="13"/>
       <c r="H21" s="12"/>
@@ -1364,7 +1365,7 @@
       <c r="B22" s="23"/>
       <c r="C22" s="20"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -1390,7 +1391,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="23"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10" t="s">
@@ -1422,7 +1423,7 @@
       <c r="B24" s="27"/>
       <c r="C24" s="23"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="E24" s="21"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1450,7 +1451,7 @@
       <c r="B25" s="21"/>
       <c r="C25" s="20"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -1478,7 +1479,7 @@
       <c r="B26" s="24"/>
       <c r="C26" s="28"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="E26" s="28"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -1518,7 +1519,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1527,7 +1528,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1537,7 +1538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1638786-0405-41BD-AA37-EC68E5706618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -189,7 +188,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -303,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -328,12 +327,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -371,6 +364,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -396,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -436,9 +436,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -473,7 +473,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -508,7 +508,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,7 +681,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -713,16 +713,16 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="23" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
@@ -731,37 +731,37 @@
       <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="14" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="15" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="7" t="s">
@@ -801,8 +801,8 @@
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
@@ -829,8 +829,8 @@
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -857,8 +857,8 @@
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="23"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="21"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
@@ -885,8 +885,8 @@
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
@@ -913,8 +913,8 @@
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -941,8 +941,8 @@
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -969,13 +969,13 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="26"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="I8" s="11"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -997,8 +997,8 @@
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="23"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1027,13 +1027,13 @@
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="L10" s="10"/>
@@ -1054,8 +1054,8 @@
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -1082,13 +1082,13 @@
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -1110,8 +1110,8 @@
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1138,13 +1138,13 @@
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="20"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="18"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -1166,13 +1166,13 @@
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
@@ -1194,13 +1194,13 @@
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
@@ -1222,8 +1222,8 @@
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -1250,8 +1250,8 @@
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -1278,10 +1278,10 @@
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="20"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -1306,13 +1306,13 @@
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -1334,13 +1334,13 @@
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="10"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="12"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="28"/>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1362,13 +1362,13 @@
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
@@ -1390,8 +1390,8 @@
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10" t="s">
@@ -1420,13 +1420,13 @@
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="23"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -1448,13 +1448,13 @@
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="20"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
@@ -1476,13 +1476,13 @@
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="28"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -1507,19 +1507,19 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B29" s="18"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B30" s="19"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
+  <sortState ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1528,7 +1528,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1538,7 +1538,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -302,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -328,9 +328,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -364,13 +361,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -713,55 +709,55 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="7" t="s">
@@ -801,13 +797,13 @@
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
@@ -829,13 +825,13 @@
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="10"/>
       <c r="J3" s="10"/>
       <c r="K3" s="10"/>
@@ -857,13 +853,13 @@
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="21"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
       <c r="K4" s="10"/>
@@ -885,13 +881,13 @@
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
@@ -913,13 +909,13 @@
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
@@ -941,13 +937,13 @@
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
@@ -969,8 +965,8 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="24"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="10"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
@@ -997,13 +993,13 @@
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="21"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -1027,13 +1023,13 @@
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="10"/>
       <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="L10" s="10"/>
@@ -1054,13 +1050,13 @@
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
@@ -1082,8 +1078,8 @@
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="10"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -1110,13 +1106,13 @@
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -1138,13 +1134,13 @@
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -1166,13 +1162,13 @@
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="21"/>
+      <c r="E15" s="20"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
@@ -1194,13 +1190,13 @@
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
@@ -1222,13 +1218,13 @@
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
@@ -1250,13 +1246,13 @@
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
@@ -1278,13 +1274,13 @@
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -1306,13 +1302,13 @@
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="21"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -1334,13 +1330,13 @@
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="10"/>
-      <c r="E21" s="21"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="24"/>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1362,13 +1358,13 @@
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="18"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
@@ -1390,15 +1386,15 @@
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10" t="s">
+      <c r="E23" s="20"/>
+      <c r="F23" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
@@ -1420,13 +1416,13 @@
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="21"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="18"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
@@ -1448,13 +1444,13 @@
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="17"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
@@ -1476,13 +1472,13 @@
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="26"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="21"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -1507,13 +1503,13 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B30" s="17"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="1" t="s">
         <v>52</v>
       </c>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -302,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -367,6 +367,10 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -972,7 +976,7 @@
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="11"/>
+      <c r="I8" s="28"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
@@ -1085,7 +1089,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
-      <c r="I12" s="10"/>
+      <c r="I12" s="17"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -1141,7 +1145,7 @@
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="17"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -1169,7 +1173,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
-      <c r="I15" s="10"/>
+      <c r="I15" s="28"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
@@ -1197,7 +1201,7 @@
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="10"/>
+      <c r="I16" s="17"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
@@ -1281,7 +1285,7 @@
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="10"/>
+      <c r="I19" s="17"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
@@ -1309,7 +1313,7 @@
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
       <c r="H20" s="20"/>
-      <c r="I20" s="10"/>
+      <c r="I20" s="18"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
@@ -1337,7 +1341,7 @@
       <c r="F21" s="18"/>
       <c r="G21" s="26"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="10"/>
+      <c r="I21" s="18"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -1365,7 +1369,7 @@
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
-      <c r="I22" s="10"/>
+      <c r="I22" s="18"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -1423,7 +1427,7 @@
       <c r="F24" s="20"/>
       <c r="G24" s="18"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="10"/>
+      <c r="I24" s="18"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
@@ -1451,7 +1455,7 @@
       <c r="F25" s="17"/>
       <c r="G25" s="17"/>
       <c r="H25" s="20"/>
-      <c r="I25" s="10"/>
+      <c r="I25" s="18"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
@@ -1479,7 +1483,7 @@
       <c r="F26" s="25"/>
       <c r="G26" s="25"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B27F99F-23DA-48A1-A9F9-398B4AD07482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -188,7 +189,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -302,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -327,9 +328,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -367,10 +365,16 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -396,9 +400,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -436,9 +440,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -473,7 +477,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -508,7 +512,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,7 +685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -713,55 +717,55 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="7" t="s">
@@ -801,17 +805,17 @@
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
@@ -829,17 +833,17 @@
       <c r="A3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="10"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
@@ -857,17 +861,17 @@
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
@@ -885,17 +889,17 @@
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
@@ -913,17 +917,17 @@
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
@@ -941,17 +945,17 @@
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
@@ -969,17 +973,17 @@
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
@@ -997,17 +1001,17 @@
       <c r="A9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="20"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
       <c r="M9" s="10" t="s">
         <v>11</v>
       </c>
@@ -1027,16 +1031,17 @@
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="16"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
@@ -1054,17 +1059,17 @@
       <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
@@ -1082,17 +1087,17 @@
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="17"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
       <c r="I12" s="17"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="16"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
@@ -1110,17 +1115,17 @@
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
@@ -1138,17 +1143,17 @@
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="19"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
@@ -1166,17 +1171,17 @@
       <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="10"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
@@ -1194,17 +1199,17 @@
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
@@ -1222,17 +1227,17 @@
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
@@ -1250,17 +1255,17 @@
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
       <c r="O18" s="11"/>
@@ -1278,17 +1283,17 @@
       <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
@@ -1306,17 +1311,17 @@
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="18"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="19"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
@@ -1334,17 +1339,17 @@
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="17"/>
       <c r="D21" s="10"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="16"/>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
@@ -1362,17 +1367,17 @@
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="17"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
@@ -1390,19 +1395,19 @@
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="10"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="17" t="s">
+      <c r="E23" s="19"/>
+      <c r="F23" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
@@ -1420,17 +1425,17 @@
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="20"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="23"/>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
@@ -1448,17 +1453,17 @@
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
@@ -1476,17 +1481,17 @@
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1507,19 +1512,19 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B29" s="15"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B30" s="16"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="1" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1528,7 +1533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1538,7 +1543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\УП П-40 2027\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Boikov\testRepo\testAlexB\testRepo\УП П-40 2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B27F99F-23DA-48A1-A9F9-398B4AD07482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="П-40 2026" sheetId="1" r:id="rId1"/>
@@ -189,7 +188,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -400,9 +399,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -440,9 +439,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -477,7 +476,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -512,7 +511,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -685,7 +684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
@@ -816,7 +815,7 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
-      <c r="M2" s="10"/>
+      <c r="M2" s="16"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
@@ -844,7 +843,7 @@
       <c r="J3" s="16"/>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="10"/>
+      <c r="M3" s="16"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -872,7 +871,7 @@
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
       <c r="L4" s="16"/>
-      <c r="M4" s="10"/>
+      <c r="M4" s="16"/>
       <c r="N4" s="10"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -900,7 +899,7 @@
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="16"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -928,7 +927,7 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
       <c r="L6" s="16"/>
-      <c r="M6" s="10"/>
+      <c r="M6" s="16"/>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10"/>
@@ -956,7 +955,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="16"/>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
@@ -984,7 +983,7 @@
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
-      <c r="M8" s="10"/>
+      <c r="M8" s="16"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
@@ -1012,7 +1011,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="16" t="s">
         <v>11</v>
       </c>
       <c r="N9" s="10"/>
@@ -1042,7 +1041,7 @@
       <c r="J10" s="16"/>
       <c r="K10" s="15"/>
       <c r="L10" s="16"/>
-      <c r="M10" s="10"/>
+      <c r="M10" s="16"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
@@ -1070,7 +1069,7 @@
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="16"/>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
@@ -1098,7 +1097,7 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="16"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="16"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
@@ -1126,7 +1125,7 @@
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="16"/>
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
@@ -1154,7 +1153,7 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="19"/>
-      <c r="M14" s="10"/>
+      <c r="M14" s="16"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -1182,7 +1181,7 @@
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="16"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -1210,7 +1209,7 @@
       <c r="J16" s="16"/>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
-      <c r="M16" s="10"/>
+      <c r="M16" s="16"/>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
@@ -1238,7 +1237,7 @@
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
-      <c r="M17" s="10"/>
+      <c r="M17" s="16"/>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
@@ -1266,7 +1265,7 @@
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
-      <c r="M18" s="10"/>
+      <c r="M18" s="16"/>
       <c r="N18" s="10"/>
       <c r="O18" s="11"/>
       <c r="P18" s="10"/>
@@ -1294,7 +1293,7 @@
       <c r="J19" s="16"/>
       <c r="K19" s="16"/>
       <c r="L19" s="16"/>
-      <c r="M19" s="10"/>
+      <c r="M19" s="16"/>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
@@ -1322,7 +1321,7 @@
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
       <c r="L20" s="19"/>
-      <c r="M20" s="10"/>
+      <c r="M20" s="16"/>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
@@ -1350,7 +1349,7 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
       <c r="L21" s="16"/>
-      <c r="M21" s="10"/>
+      <c r="M21" s="16"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
@@ -1378,7 +1377,7 @@
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
-      <c r="M22" s="10"/>
+      <c r="M22" s="16"/>
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
@@ -1408,7 +1407,7 @@
       <c r="J23" s="16"/>
       <c r="K23" s="19"/>
       <c r="L23" s="19"/>
-      <c r="M23" s="10"/>
+      <c r="M23" s="16"/>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
@@ -1436,7 +1435,7 @@
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
       <c r="L24" s="23"/>
-      <c r="M24" s="10"/>
+      <c r="M24" s="16"/>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
       <c r="P24" s="10"/>
@@ -1464,7 +1463,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
-      <c r="M25" s="10"/>
+      <c r="M25" s="16"/>
       <c r="N25" s="10"/>
       <c r="O25" s="10"/>
       <c r="P25" s="10"/>
@@ -1492,7 +1491,7 @@
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
-      <c r="M26" s="3"/>
+      <c r="M26" s="27"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -1524,7 +1523,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A25">
+  <sortState ref="A2:A25">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1533,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1543,7 +1542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/УП П-40 2027/Состояние УП 01.xlsx
+++ b/УП П-40 2027/Состояние УП 01.xlsx
@@ -840,10 +840,10 @@
       <c r="G3" s="19"/>
       <c r="H3" s="19"/>
       <c r="I3" s="19"/>
-      <c r="J3" s="16"/>
+      <c r="J3" s="19"/>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="16"/>
+      <c r="M3" s="19"/>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -899,7 +899,7 @@
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
-      <c r="M5" s="16"/>
+      <c r="M5" s="19"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -983,7 +983,7 @@
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="M8" s="17"/>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
@@ -1008,7 +1008,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19"/>
-      <c r="J9" s="22"/>
+      <c r="J9" s="29"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19"/>
       <c r="M9" s="16" t="s">
@@ -1097,7 +1097,7 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="M12" s="17"/>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
@@ -1153,7 +1153,7 @@
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
       <c r="L14" s="19"/>
-      <c r="M14" s="16"/>
+      <c r="M14" s="19"/>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -1180,8 +1180,8 @@
       <c r="I15" s="29"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
       <c r="N15" s="10"/>
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
@@ -1348,8 +1348,8 @@
       <c r="I21" s="19"/>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
@@ -1404,10 +1404,10 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="16"/>
+      <c r="J23" s="19"/>
       <c r="K23" s="19"/>
       <c r="L23" s="19"/>
-      <c r="M23" s="16"/>
+      <c r="M23" s="19"/>
       <c r="N23" s="10"/>
       <c r="O23" s="10"/>
       <c r="P23" s="10"/>
@@ -1523,8 +1523,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:A25">
-    <sortCondition ref="A2"/>
+  <sortState ref="A2:Y26">
+    <sortCondition ref="C2:C26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
